--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:14</t>
+    <t xml:space="preserve">2026-09-09 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:08</t>
+    <t xml:space="preserve">2026-09-17 14:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:05</t>
+    <t xml:space="preserve">2026-09-23 12:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:34</t>
+    <t xml:space="preserve">2026-10-02 13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:58</t>
+    <t xml:space="preserve">2026-10-04 08:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:58</t>
+    <t xml:space="preserve">2026-10-05 10:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -525,7 +525,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>292500.62</v>
+        <v>292500.63</v>
       </c>
     </row>
     <row r="4">
